--- a/output/laminas_comunales/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: O'Higgins (112,8).</t>
         </is>
       </c>
     </row>
